--- a/diseases/d236/2005-2009.xlsx
+++ b/diseases/d236/2005-2009.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>27</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.5840206751971178</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>41</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.8868462104845123</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>29</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.6272814659524598</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>34</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.7354334428408149</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>38</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.8219550243514991</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>37</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.8003246289738281</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>38</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.8219550243514991</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>55</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>1.189671745771907</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>35</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.757063838218486</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>41</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.8868462104845123</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>56</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>1.211302141149578</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>39</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.8435854197291701</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>47</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>1.00847678379159</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>38</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.8153642081719235</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>38</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.8153642081719235</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>43</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.9226489724050713</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>66</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>1.416158887877551</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>60</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>1.287417170797774</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>39</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.836821161018553</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>89</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>1.909668803350031</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>52</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>1.115761548024737</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>54</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>1.158675453717996</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>54</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>1.158675453717996</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>50</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>1.072847642331478</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>63</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>1.337860824249683</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>47</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.9980866466624619</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>37</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.7857277856704489</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>27</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.5733689246784356</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>45</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.9556148744640593</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>31</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.6583124690752409</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>55</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>1.167973735456072</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>64</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>1.359096710348884</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>57</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>1.210445507654475</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>78</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>1.656399115737703</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>56</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>1.189209621555274</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>44</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.9343789883648581</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>48</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>1.006690084794764</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>71</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>1.489062417092255</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>54</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>1.13252634539411</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>44</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.9227992443952006</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>50</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>1.048635504994546</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>60</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.258362605993455</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>58</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>1.216417185793673</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>58</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>1.216417185793673</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>64</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>1.342253446393019</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>54</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.13252634539411</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>42</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.8808538241954187</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>53</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>1.111553635294219</v>
       </c>
@@ -20012,9 +19868,6 @@
       <c r="O99" t="n">
         <v>65</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>1.34613960813876</v>
       </c>
@@ -20408,9 +20261,6 @@
       <c r="O101" t="n">
         <v>63</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>1.304719927888337</v>
       </c>
@@ -20804,9 +20654,6 @@
       <c r="O103" t="n">
         <v>68</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>1.408269128514395</v>
       </c>
@@ -21200,9 +21047,6 @@
       <c r="O105" t="n">
         <v>69</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>1.428978968639607</v>
       </c>
@@ -21596,9 +21440,6 @@
       <c r="O107" t="n">
         <v>63</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>1.304719927888337</v>
       </c>
@@ -21992,9 +21833,6 @@
       <c r="O109" t="n">
         <v>74</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>1.532528169265665</v>
       </c>
@@ -22388,9 +22226,6 @@
       <c r="O111" t="n">
         <v>88</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>1.822465931018629</v>
       </c>
@@ -22784,9 +22619,6 @@
       <c r="O113" t="n">
         <v>80</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>1.656787210016935</v>
       </c>
@@ -23180,9 +23012,6 @@
       <c r="O115" t="n">
         <v>72</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>1.491108489015242</v>
       </c>
@@ -23576,9 +23405,6 @@
       <c r="O117" t="n">
         <v>68</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>1.408269128514395</v>
       </c>
@@ -23972,9 +23798,6 @@
       <c r="O119" t="n">
         <v>57</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>1.180460887137067</v>
       </c>
@@ -24367,9 +24190,6 @@
       </c>
       <c r="O121" t="n">
         <v>51</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>0</v>
       </c>
       <c r="R121" t="n">
         <v>1.056201846385796</v>
